--- a/report/downloads/reports/网点变化对比报告_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525.xlsx
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>东塘路80号合肥巢湖万达广场1F</t>
+          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区万象汇</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
+          <t>东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
+          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武侯大道顺江段61号</t>
+          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都惠王陵西路</t>
+          <t>鸿蒙智行智界用户中心•成都武侯大道</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市龙泉驿区惠王陵西路155号</t>
+          <t>四川省成都市武侯区武侯大道顺江段61号</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
     </row>
@@ -13123,22 +13123,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13148,29 +13148,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13224,17 +13224,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13276,29 +13276,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13308,29 +13308,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•六安万达广场</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13372,29 +13372,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13404,29 +13404,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13436,29 +13436,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波马径汽车园</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区压赛堰路666号 → 浙江省宁波市江北区压赛堰路666号（马径汽车园）</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13507,22 +13507,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13532,29 +13532,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13564,29 +13564,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13596,29 +13596,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13628,29 +13628,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•六安万达广场</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13660,29 +13660,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区皋城路与八公山北路交汇处万达广场1AF29-30 → 安徽省六安市金安区万达广场1A层29-30商铺</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13692,29 +13692,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13724,29 +13724,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13756,29 +13756,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13820,14 +13820,14 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13852,29 +13852,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13916,29 +13916,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13948,29 +13948,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>南宁市青秀区云景路28号南宁日报社 → 广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业）</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13992,17 +13992,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14012,29 +14012,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14044,29 +14044,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14076,29 +14076,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14108,29 +14108,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -14152,17 +14152,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•海口椰海大道</t>
+          <t>鸿蒙智行授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市秀英区秀英街道椰海大道370号A2铺 → 海南省海口市秀英区秀英街道椰海大道370号（临时营业）</t>
+          <t>贵州省黔南布依族苗族自治州都匀市毛尖大道茂盛汽车城 → 贵州省黔南布依族苗族自治州都匀市沙包堡街道纬八西路羊场坝茂盛汽车城11号仓库</t>
         </is>
       </c>
     </row>
@@ -14216,17 +14216,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14248,17 +14248,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14312,17 +14312,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14339,22 +14339,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14371,22 +14371,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14600,17 +14600,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14632,17 +14632,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14659,7 +14659,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -14669,12 +14669,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14728,17 +14728,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14792,17 +14792,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14824,17 +14824,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14888,17 +14888,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14920,17 +14920,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15048,17 +15048,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15112,17 +15112,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15144,17 +15144,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15208,17 +15208,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15240,17 +15240,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15432,17 +15432,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15496,17 +15496,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15528,17 +15528,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15560,17 +15560,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15656,17 +15656,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15688,17 +15688,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15747,22 +15747,22 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15843,22 +15843,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15880,17 +15880,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15912,17 +15912,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16072,17 +16072,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16104,17 +16104,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16136,17 +16136,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16168,17 +16168,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16200,17 +16200,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16232,17 +16232,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16296,17 +16296,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16323,22 +16323,22 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16355,22 +16355,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16397,12 +16397,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16419,22 +16419,22 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16579,22 +16579,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16675,22 +16675,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16963,22 +16963,22 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -16995,22 +16995,22 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17059,22 +17059,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17091,22 +17091,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17219,22 +17219,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17512,17 +17512,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17571,22 +17571,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17613,12 +17613,12 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17640,17 +17640,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17672,17 +17672,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17704,17 +17704,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17768,17 +17768,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17800,17 +17800,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17832,17 +17832,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17891,22 +17891,22 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17928,17 +17928,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -17992,17 +17992,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18024,17 +18024,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18056,17 +18056,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18088,17 +18088,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18120,17 +18120,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18152,17 +18152,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18211,22 +18211,22 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18248,17 +18248,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18275,22 +18275,22 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18312,17 +18312,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18339,22 +18339,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18376,17 +18376,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18403,22 +18403,22 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18440,17 +18440,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18472,17 +18472,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18504,17 +18504,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18536,17 +18536,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -18728,17 +18728,17 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18760,17 +18760,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -18792,17 +18792,17 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -18812,29 +18812,29 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18856,17 +18856,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18888,17 +18888,17 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18920,17 +18920,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18952,17 +18952,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18984,17 +18984,17 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -19011,22 +19011,22 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -19053,12 +19053,12 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
